--- a/desocupados_mjj2026.xlsx
+++ b/desocupados_mjj2026.xlsx
@@ -13,24 +13,25 @@
     <sheet name="Sexo" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Edad" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Region" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Educacion" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Nacionalidad" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Pueblo_indigena" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Jefatura_hogar" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Condicion" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Duracion_busqueda" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="Duracion_cesantia" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="Motivo_termino" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="Motivo_despido" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="Motivo_renuncia" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="Jornada_buscada" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="Metodos_busqueda" sheetId="17" state="visible" r:id="rId19"/>
-    <sheet name="Panel_situacion_2025" sheetId="18" state="visible" r:id="rId20"/>
-    <sheet name="Panel_rama_2025" sheetId="19" state="visible" r:id="rId21"/>
-    <sheet name="Panel_contrato_2025" sheetId="20" state="visible" r:id="rId22"/>
-    <sheet name="Panel_categoria_2025" sheetId="21" state="visible" r:id="rId23"/>
-    <sheet name="Panel_formalidad_2025" sheetId="22" state="visible" r:id="rId24"/>
-    <sheet name="Panel_sector_inst_2025" sheetId="23" state="visible" r:id="rId25"/>
+    <sheet name="Provincia" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Educacion" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Nacionalidad" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Pueblo_indigena" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Jefatura_hogar" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Condicion" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Duracion_busqueda" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Duracion_cesantia" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Motivo_termino" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Motivo_despido" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="Motivo_renuncia" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="Jornada_buscada" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="Metodos_busqueda" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="Panel_situacion_2025" sheetId="19" state="visible" r:id="rId21"/>
+    <sheet name="Panel_rama_2025" sheetId="20" state="visible" r:id="rId22"/>
+    <sheet name="Panel_contrato_2025" sheetId="21" state="visible" r:id="rId23"/>
+    <sheet name="Panel_categoria_2025" sheetId="22" state="visible" r:id="rId24"/>
+    <sheet name="Panel_formalidad_2025" sheetId="23" state="visible" r:id="rId25"/>
+    <sheet name="Panel_sector_inst_2025" sheetId="24" state="visible" r:id="rId26"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="292">
   <si>
     <t xml:space="preserve">Caracterización de las personas desocupadas - ENE, trimestre móvil mayo-junio-julio 2026</t>
   </si>
@@ -330,6 +331,168 @@
   </si>
   <si>
     <t xml:space="preserve">Magallanes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personas desocupadas según provincia - MJJ 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arica (Arica y Parinacota)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parinacota (Arica y Parinacota)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iquique (Tarapacá)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamarugal (Tarapacá)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antofagasta (Antofagasta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Loa (Antofagasta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tocopilla (Antofagasta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copiapó (Atacama)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chañaral (Atacama)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huasco (Atacama)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elqui (Coquimbo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choapa (Coquimbo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limarí (Coquimbo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso (Valparaíso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Andes (Valparaíso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petorca (Valparaíso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillota (Valparaíso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio (Valparaíso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Felipe de Aconcagua (Valparaíso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marga Marga (Valparaíso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santiago (Metropolitana)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cordillera (Metropolitana)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chacabuco (Metropolitana)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maipo (Metropolitana)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipilla (Metropolitana)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talagante (Metropolitana)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cachapoal (O'Higgins)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cardenal Caro (O'Higgins)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colchagua (O'Higgins)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talca (Maule)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cauquenes (Maule)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curicó (Maule)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linares (Maule)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diguillín (Ñuble)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Itata (Ñuble)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punilla (Ñuble)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concepción (Biobío)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arauco (Biobío)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biobío (Biobío)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cautín (La Araucanía)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malleco (La Araucanía)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valdivia (Los Ríos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranco (Los Ríos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llanquihue (Los Lagos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiloé (Los Lagos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osorno (Los Lagos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coyhaique (Aysén)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aysén (Aysén)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Carrera (Aysén)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magallanes (Magallanes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tierra del Fuego (Magallanes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Última Esperanza (Magallanes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota: Nota: la ENE tiene representatividad regional, no provincial. Estas cifras son elaboración propia y no constituyen estimaciones oficiales del INE: en varias provincias el número de casos muestrales de personas desocupadas es muy bajo y la tasa resultante tiene un error muestral alto. Las provincias de Isla de Pascua y Palena no aparecen porque no forman parte de la muestra del trimestre. El nombre de cada provincia va acompañado de su región.</t>
   </si>
   <si>
     <t xml:space="preserve">Personas desocupadas según nivel educacional alcanzado - MJJ 2026</t>
@@ -1461,16 +1624,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1486,35 +1649,55 @@
       <c r="D3" s="6" t="s">
         <v>62</v>
       </c>
+      <c r="E3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3984</v>
+        <v>1343</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>893873</v>
+        <v>301672</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">IFERROR(C4/$C$6*100,"")</f>
-        <v>91.1144658139696</v>
+        <v>30.7500988742605</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>5537482</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <f aca="false">IFERROR(C4/E4*100,"")</f>
+        <v>5.44781906288815</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>428</v>
+        <v>3069</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>87171</v>
+        <v>679372</v>
       </c>
       <c r="D5" s="5" t="n">
         <f aca="false">IFERROR(C5/$C$6*100,"")</f>
-        <v>8.88553418603039</v>
+        <v>69.2499011257395</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>4757579</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <f aca="false">IFERROR(C5/E5*100,"")</f>
+        <v>14.2797838984912</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1532,6 +1715,14 @@
       <c r="D6" s="9" t="n">
         <f aca="false">SUM(D4:D5)</f>
         <v>100</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <f aca="false">SUM(E4:E5)</f>
+        <v>10295061</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <f aca="false">IFERROR(C6/E6*100,"")</f>
+        <v>9.52926845212476</v>
       </c>
     </row>
   </sheetData>
@@ -1550,7 +1741,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -1559,7 +1750,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1578,114 +1769,49 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1784</v>
+        <v>3984</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>391840</v>
+        <v>893873</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">IFERROR(C4/$C$10*100,"")</f>
-        <v>39.9411239455111</v>
+        <f aca="false">IFERROR(C4/$C$6*100,"")</f>
+        <v>91.1144658139696</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1149</v>
+        <v>428</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>260023</v>
+        <v>87171</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">IFERROR(C5/$C$10*100,"")</f>
-        <v>26.5047235394131</v>
+        <f aca="false">IFERROR(C5/$C$6*100,"")</f>
+        <v>8.88553418603039</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>519</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>125105</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <f aca="false">IFERROR(C6/$C$10*100,"")</f>
-        <v>12.7522312964556</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>440</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>95087</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <f aca="false">IFERROR(C7/$C$10*100,"")</f>
-        <v>9.69242969734283</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>262</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>53611</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <f aca="false">IFERROR(C8/$C$10*100,"")</f>
-        <v>5.46468863781849</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>258</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>55378</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <f aca="false">IFERROR(C9/$C$10*100,"")</f>
-        <v>5.64480288345885</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="8" t="n">
-        <f aca="false">SUM(B4:B9)</f>
+      <c r="B6" s="8" t="n">
+        <f aca="false">SUM(B4:B5)</f>
         <v>4412</v>
       </c>
-      <c r="C10" s="8" t="n">
-        <f aca="false">SUM(C4:C9)</f>
+      <c r="C6" s="8" t="n">
+        <f aca="false">SUM(C4:C5)</f>
         <v>981044</v>
       </c>
-      <c r="D10" s="9" t="n">
-        <f aca="false">SUM(D4:D9)</f>
+      <c r="D6" s="9" t="n">
+        <f aca="false">SUM(D4:D5)</f>
         <v>100</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1713,7 +1839,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1732,92 +1858,92 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1239</v>
+        <v>1784</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>282695</v>
+        <v>391840</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">IFERROR(C4/$C$10*100,"")</f>
-        <v>31.62589274527</v>
+        <v>39.9411239455111</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>965</v>
+        <v>1149</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>216249</v>
+        <v>260023</v>
       </c>
       <c r="D5" s="5" t="n">
         <f aca="false">IFERROR(C5/$C$10*100,"")</f>
-        <v>24.1923899618737</v>
+        <v>26.5047235394131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>588</v>
+        <v>519</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>133397</v>
+        <v>125105</v>
       </c>
       <c r="D6" s="5" t="n">
         <f aca="false">IFERROR(C6/$C$10*100,"")</f>
-        <v>14.9235013514239</v>
+        <v>12.7522312964556</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>103250</v>
+        <v>95087</v>
       </c>
       <c r="D7" s="5" t="n">
         <f aca="false">IFERROR(C7/$C$10*100,"")</f>
-        <v>11.5508708181932</v>
+        <v>9.69242969734283</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>58867</v>
+        <v>53611</v>
       </c>
       <c r="D8" s="5" t="n">
         <f aca="false">IFERROR(C8/$C$10*100,"")</f>
-        <v>6.58561852256251</v>
+        <v>5.46468863781849</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>458</v>
+        <v>258</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>99414</v>
+        <v>55378</v>
       </c>
       <c r="D9" s="5" t="n">
         <f aca="false">IFERROR(C9/$C$10*100,"")</f>
-        <v>11.1217266006766</v>
+        <v>5.64480288345885</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1826,11 +1952,11 @@
       </c>
       <c r="B10" s="8" t="n">
         <f aca="false">SUM(B4:B9)</f>
-        <v>3984</v>
+        <v>4412</v>
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">SUM(C4:C9)</f>
-        <v>893872</v>
+        <v>981044</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">SUM(D4:D9)</f>
@@ -1839,7 +1965,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -1858,7 +1984,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -1867,7 +1993,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1886,189 +2012,114 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>671</v>
+        <v>1239</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>167717</v>
+        <v>282695</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">IFERROR(C4/$C$15*100,"")</f>
-        <v>18.7629772495391</v>
+        <f aca="false">IFERROR(C4/$C$10*100,"")</f>
+        <v>31.62589274527</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>561</v>
+        <v>965</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>134450</v>
+        <v>216249</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">IFERROR(C5/$C$15*100,"")</f>
-        <v>15.0413034528434</v>
+        <f aca="false">IFERROR(C5/$C$10*100,"")</f>
+        <v>24.1923899618737</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2439</v>
+        <v>588</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>523025</v>
+        <v>133397</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">IFERROR(C6/$C$15*100,"")</f>
-        <v>58.5122925877531</v>
+        <f aca="false">IFERROR(C6/$C$10*100,"")</f>
+        <v>14.9235013514239</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>35</v>
+        <v>449</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7324</v>
+        <v>103250</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">IFERROR(C7/$C$15*100,"")</f>
-        <v>0.819356686415952</v>
+        <f aca="false">IFERROR(C7/$C$10*100,"")</f>
+        <v>11.5508708181932</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>181</v>
+        <v>285</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>40692</v>
+        <v>58867</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">IFERROR(C8/$C$15*100,"")</f>
-        <v>4.55232964003795</v>
+        <f aca="false">IFERROR(C8/$C$10*100,"")</f>
+        <v>6.58561852256251</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>62</v>
+        <v>458</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>13823</v>
+        <v>99414</v>
       </c>
       <c r="D9" s="5" t="n">
-        <f aca="false">IFERROR(C9/$C$15*100,"")</f>
-        <v>1.54641827912721</v>
+        <f aca="false">IFERROR(C9/$C$10*100,"")</f>
+        <v>11.1217266006766</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1751</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <f aca="false">IFERROR(C10/$C$15*100,"")</f>
-        <v>0.195889344335654</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>2118</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <f aca="false">IFERROR(C11/$C$15*100,"")</f>
-        <v>0.236946676929135</v>
+      <c r="A10" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <f aca="false">SUM(B4:B9)</f>
+        <v>3984</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <f aca="false">SUM(C4:C9)</f>
+        <v>893872</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <f aca="false">SUM(D4:D9)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>168</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <f aca="false">IFERROR(C12/$C$15*100,"")</f>
-        <v>0.0187946372635008</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>2157</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <f aca="false">IFERROR(C13/$C$15*100,"")</f>
-        <v>0.241309717722448</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>647</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <f aca="false">IFERROR(C14/$C$15*100,"")</f>
-        <v>0.072381728032649</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="8" t="n">
-        <f aca="false">SUM(B4:B14)</f>
-        <v>3984</v>
-      </c>
-      <c r="C15" s="8" t="n">
-        <f aca="false">SUM(C4:C14)</f>
-        <v>893872</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <f aca="false">SUM(D4:D14)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>140</v>
+      <c r="A12" s="10" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2087,7 +2138,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -2096,7 +2147,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2115,204 +2166,189 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2</v>
+        <v>671</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>246</v>
+        <v>167717</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">IFERROR(C4/$C$16*100,"")</f>
-        <v>0.146675650053364</v>
+        <f aca="false">IFERROR(C4/$C$15*100,"")</f>
+        <v>18.7629772495391</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>18</v>
+        <v>561</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>6305</v>
+        <v>134450</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">IFERROR(C5/$C$16*100,"")</f>
-        <v>3.75930883571731</v>
+        <f aca="false">IFERROR(C5/$C$15*100,"")</f>
+        <v>15.0413034528434</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5</v>
+        <v>2439</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>689</v>
+        <v>523025</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">IFERROR(C6/$C$16*100,"")</f>
-        <v>0.410811068645397</v>
+        <f aca="false">IFERROR(C6/$C$15*100,"")</f>
+        <v>58.5122925877531</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>13472</v>
+        <v>7324</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">IFERROR(C7/$C$16*100,"")</f>
-        <v>8.03257868910128</v>
+        <f aca="false">IFERROR(C7/$C$15*100,"")</f>
+        <v>0.819356686415952</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>6</v>
+        <v>181</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1114</v>
+        <v>40692</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">IFERROR(C8/$C$16*100,"")</f>
-        <v>0.664214122599379</v>
+        <f aca="false">IFERROR(C8/$C$15*100,"")</f>
+        <v>4.55232964003795</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5279</v>
+        <v>13823</v>
       </c>
       <c r="D9" s="5" t="n">
-        <f aca="false">IFERROR(C9/$C$16*100,"")</f>
-        <v>3.1475640513484</v>
+        <f aca="false">IFERROR(C9/$C$15*100,"")</f>
+        <v>1.54641827912721</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1067</v>
+        <v>1751</v>
       </c>
       <c r="D10" s="5" t="n">
-        <f aca="false">IFERROR(C10/$C$16*100,"")</f>
-        <v>0.636190726044468</v>
+        <f aca="false">IFERROR(C10/$C$15*100,"")</f>
+        <v>0.195889344335654</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>473</v>
+        <v>13</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>123893</v>
+        <v>2118</v>
       </c>
       <c r="D11" s="5" t="n">
-        <f aca="false">IFERROR(C11/$C$16*100,"")</f>
-        <v>73.8702695612252</v>
+        <f aca="false">IFERROR(C11/$C$15*100,"")</f>
+        <v>0.236946676929135</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2491</v>
+        <v>168</v>
       </c>
       <c r="D12" s="5" t="n">
-        <f aca="false">IFERROR(C12/$C$16*100,"")</f>
-        <v>1.48524001741028</v>
+        <f aca="false">IFERROR(C12/$C$15*100,"")</f>
+        <v>0.0187946372635008</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>10802</v>
+        <v>2157</v>
       </c>
       <c r="D13" s="5" t="n">
-        <f aca="false">IFERROR(C13/$C$16*100,"")</f>
-        <v>6.44061126779038</v>
+        <f aca="false">IFERROR(C13/$C$15*100,"")</f>
+        <v>0.241309717722448</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1678</v>
+        <v>647</v>
       </c>
       <c r="D14" s="5" t="n">
-        <f aca="false">IFERROR(C14/$C$16*100,"")</f>
-        <v>1.00049488125831</v>
+        <f aca="false">IFERROR(C14/$C$15*100,"")</f>
+        <v>0.072381728032649</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>681</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <f aca="false">IFERROR(C15/$C$16*100,"")</f>
-        <v>0.406041128806263</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="A15" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="8" t="n">
-        <f aca="false">SUM(B4:B15)</f>
-        <v>671</v>
-      </c>
-      <c r="C16" s="8" t="n">
-        <f aca="false">SUM(C4:C15)</f>
-        <v>167717</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <f aca="false">SUM(D4:D15)</f>
+      <c r="B15" s="8" t="n">
+        <f aca="false">SUM(B4:B14)</f>
+        <v>3984</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <f aca="false">SUM(C4:C14)</f>
+        <v>893872</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <f aca="false">SUM(D4:D14)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>152</v>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2340,7 +2376,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2359,182 +2395,182 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>12497</v>
+        <v>246</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">IFERROR(C4/$C$16*100,"")</f>
-        <v>9.29490516920789</v>
+        <v>0.146675650053364</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>155</v>
+        <v>197</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>24326</v>
+        <v>6305</v>
       </c>
       <c r="D5" s="5" t="n">
         <f aca="false">IFERROR(C5/$C$16*100,"")</f>
-        <v>18.0929713648196</v>
+        <v>3.75930883571731</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>18333</v>
+        <v>689</v>
       </c>
       <c r="D6" s="5" t="n">
         <f aca="false">IFERROR(C6/$C$16*100,"")</f>
-        <v>13.635552249907</v>
+        <v>0.410811068645397</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6609</v>
+        <v>13472</v>
       </c>
       <c r="D7" s="5" t="n">
         <f aca="false">IFERROR(C7/$C$16*100,"")</f>
-        <v>4.91558200074377</v>
+        <v>8.03257868910128</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>11959</v>
+        <v>1114</v>
       </c>
       <c r="D8" s="5" t="n">
         <f aca="false">IFERROR(C8/$C$16*100,"")</f>
-        <v>8.89475641502417</v>
+        <v>0.664214122599379</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>159</v>
+        <v>201</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>12279</v>
+        <v>5279</v>
       </c>
       <c r="D9" s="5" t="n">
         <f aca="false">IFERROR(C9/$C$16*100,"")</f>
-        <v>9.13276310896244</v>
+        <v>3.1475640513484</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4359</v>
+        <v>1067</v>
       </c>
       <c r="D10" s="5" t="n">
         <f aca="false">IFERROR(C10/$C$16*100,"")</f>
-        <v>3.24209743399033</v>
+        <v>0.636190726044468</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>68</v>
+        <v>473</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>18917</v>
+        <v>123893</v>
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">IFERROR(C11/$C$16*100,"")</f>
-        <v>14.0699144663444</v>
+        <v>73.8702695612252</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>150</v>
+        <v>204</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>493</v>
+        <v>2491</v>
       </c>
       <c r="D12" s="5" t="n">
         <f aca="false">IFERROR(C12/$C$16*100,"")</f>
-        <v>0.366679062848643</v>
+        <v>1.48524001741028</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>151</v>
+        <v>205</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>24219</v>
+        <v>10802</v>
       </c>
       <c r="D13" s="5" t="n">
         <f aca="false">IFERROR(C13/$C$16*100,"")</f>
-        <v>18.013387876534</v>
+        <v>6.44061126779038</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>138</v>
+        <v>192</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>121</v>
+        <v>1678</v>
       </c>
       <c r="D14" s="5" t="n">
         <f aca="false">IFERROR(C14/$C$16*100,"")</f>
-        <v>0.0899962811454072</v>
+        <v>1.00049488125831</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>338</v>
+        <v>681</v>
       </c>
       <c r="D15" s="5" t="n">
         <f aca="false">IFERROR(C15/$C$16*100,"")</f>
-        <v>0.251394570472295</v>
+        <v>0.406041128806263</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2543,11 +2579,11 @@
       </c>
       <c r="B16" s="8" t="n">
         <f aca="false">SUM(B4:B15)</f>
-        <v>561</v>
+        <v>671</v>
       </c>
       <c r="C16" s="8" t="n">
         <f aca="false">SUM(C4:C15)</f>
-        <v>134450</v>
+        <v>167717</v>
       </c>
       <c r="D16" s="9" t="n">
         <f aca="false">SUM(D4:D15)</f>
@@ -2556,7 +2592,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -2575,7 +2611,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -2584,7 +2620,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2603,94 +2639,204 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>164</v>
+        <v>208</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1881</v>
+        <v>65</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>440047</v>
+        <v>12497</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">IFERROR(C4/$C$9*100,"")</f>
-        <v>44.855016548714</v>
+        <f aca="false">IFERROR(C4/$C$16*100,"")</f>
+        <v>9.29490516920789</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>554</v>
+        <v>106</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>131819</v>
+        <v>24326</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">IFERROR(C5/$C$9*100,"")</f>
-        <v>13.4366179667966</v>
+        <f aca="false">IFERROR(C5/$C$16*100,"")</f>
+        <v>18.0929713648196</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1876</v>
+        <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>386909</v>
+        <v>18333</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">IFERROR(C6/$C$9*100,"")</f>
-        <v>39.4385363332698</v>
+        <f aca="false">IFERROR(C6/$C$16*100,"")</f>
+        <v>13.635552249907</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>138</v>
+        <v>211</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4091</v>
+        <v>6609</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">IFERROR(C7/$C$9*100,"")</f>
-        <v>0.417005166949869</v>
+        <f aca="false">IFERROR(C7/$C$16*100,"")</f>
+        <v>4.91558200074377</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>139</v>
+        <v>212</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>18177</v>
+        <v>11959</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">IFERROR(C8/$C$9*100,"")</f>
-        <v>1.8528239842698</v>
+        <f aca="false">IFERROR(C8/$C$16*100,"")</f>
+        <v>8.89475641502417</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>12279</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <f aca="false">IFERROR(C9/$C$16*100,"")</f>
+        <v>9.13276310896244</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>4359</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <f aca="false">IFERROR(C10/$C$16*100,"")</f>
+        <v>3.24209743399033</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>18917</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <f aca="false">IFERROR(C11/$C$16*100,"")</f>
+        <v>14.0699144663444</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>493</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <f aca="false">IFERROR(C12/$C$16*100,"")</f>
+        <v>0.366679062848643</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>24219</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <f aca="false">IFERROR(C13/$C$16*100,"")</f>
+        <v>18.013387876534</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>121</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <f aca="false">IFERROR(C14/$C$16*100,"")</f>
+        <v>0.0899962811454072</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>338</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <f aca="false">IFERROR(C15/$C$16*100,"")</f>
+        <v>0.251394570472295</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="8" t="n">
-        <f aca="false">SUM(B4:B8)</f>
-        <v>4412</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <f aca="false">SUM(C4:C8)</f>
-        <v>981043</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <f aca="false">SUM(D4:D8)</f>
+      <c r="B16" s="8" t="n">
+        <f aca="false">SUM(B4:B15)</f>
+        <v>561</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <f aca="false">SUM(C4:C15)</f>
+        <v>134450</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <f aca="false">SUM(D4:D15)</f>
         <v>100</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -2709,7 +2855,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -2718,7 +2864,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2737,203 +2883,94 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2887</v>
+        <v>1881</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>617475</v>
+        <v>440047</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">IFERROR(C4/$C$16*100,"")</f>
-        <v>62.9406020525073</v>
+        <f aca="false">IFERROR(C4/$C$9*100,"")</f>
+        <v>44.855016548714</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>169</v>
+        <v>219</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2212</v>
+        <v>554</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>540749</v>
+        <v>131819</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">IFERROR(C5/$C$16*100,"")</f>
-        <v>55.1197499806329</v>
+        <f aca="false">IFERROR(C5/$C$9*100,"")</f>
+        <v>13.4366179667966</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1855</v>
+        <v>1876</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>387949</v>
+        <v>386909</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">IFERROR(C6/$C$16*100,"")</f>
-        <v>39.544505649084</v>
+        <f aca="false">IFERROR(C6/$C$9*100,"")</f>
+        <v>39.4385363332698</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1618</v>
+        <v>10</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>325885</v>
+        <v>4091</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">IFERROR(C7/$C$16*100,"")</f>
-        <v>33.2181838938926</v>
+        <f aca="false">IFERROR(C7/$C$9*100,"")</f>
+        <v>0.417005166949869</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>496</v>
+        <v>91</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>110247</v>
+        <v>18177</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">IFERROR(C8/$C$16*100,"")</f>
-        <v>11.2377222632216</v>
+        <f aca="false">IFERROR(C8/$C$9*100,"")</f>
+        <v>1.8528239842698</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>188</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>48837</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <f aca="false">IFERROR(C9/$C$16*100,"")</f>
-        <v>4.97806418468489</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>126</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>40703</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <f aca="false">IFERROR(C10/$C$16*100,"")</f>
-        <v>4.14894744782089</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>172</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>36900</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <f aca="false">IFERROR(C11/$C$16*100,"")</f>
-        <v>3.76129918739628</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>22362</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <f aca="false">IFERROR(C12/$C$16*100,"")</f>
-        <v>2.27940846689853</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>18795</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <f aca="false">IFERROR(C13/$C$16*100,"")</f>
-        <v>1.91581621211689</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>8603</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <f aca="false">IFERROR(C14/$C$16*100,"")</f>
-        <v>0.876922951468028</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <f aca="false">IFERROR(C15/$C$16*100,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="B16" s="8" t="n">
+      <c r="A9" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <f aca="false">SUM(B4:B8)</f>
         <v>4412</v>
       </c>
-      <c r="C16" s="8" t="n">
-        <f aca="false">Resumen!B7</f>
-        <v>981044</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <f aca="false">IFERROR(C16/$C$16*100,"")</f>
+      <c r="C9" s="8" t="n">
+        <f aca="false">SUM(C4:C8)</f>
+        <v>981043</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <f aca="false">SUM(D4:D8)</f>
         <v>100</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2952,7 +2989,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -2961,7 +2998,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2975,104 +3012,208 @@
         <v>52</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>183</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>491</v>
+        <v>2887</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>102369</v>
+        <v>617475</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">IFERROR(C4/$C$9*100,"")</f>
-        <v>46.2371273712737</v>
+        <f aca="false">IFERROR(C4/$C$16*100,"")</f>
+        <v>62.9406020525073</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>212</v>
+        <v>2212</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>48473</v>
+        <v>540749</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">IFERROR(C5/$C$9*100,"")</f>
-        <v>21.8938572719061</v>
+        <f aca="false">IFERROR(C5/$C$16*100,"")</f>
+        <v>55.1197499806329</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>186</v>
+        <v>224</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>15</v>
+        <v>1855</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2306</v>
+        <v>387949</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">IFERROR(C6/$C$9*100,"")</f>
-        <v>1.04155374887082</v>
+        <f aca="false">IFERROR(C6/$C$16*100,"")</f>
+        <v>39.544505649084</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>179</v>
+        <v>1618</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>32260</v>
+        <v>325885</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">IFERROR(C7/$C$9*100,"")</f>
-        <v>14.5709123757904</v>
+        <f aca="false">IFERROR(C7/$C$16*100,"")</f>
+        <v>33.2181838938926</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>496</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>110247</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <f aca="false">IFERROR(C8/$C$16*100,"")</f>
+        <v>11.2377222632216</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B9" s="4" t="n">
         <v>188</v>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>189</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>35992</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <f aca="false">IFERROR(C8/$C$9*100,"")</f>
-        <v>16.256549232159</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="8" t="n">
-        <f aca="false">SUM(B4:B8)</f>
-        <v>1086</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <f aca="false">SUM(C4:C8)</f>
-        <v>221400</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <f aca="false">SUM(D4:D8)</f>
+      <c r="C9" s="4" t="n">
+        <v>48837</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <f aca="false">IFERROR(C9/$C$16*100,"")</f>
+        <v>4.97806418468489</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>40703</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <f aca="false">IFERROR(C10/$C$16*100,"")</f>
+        <v>4.14894744782089</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>36900</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <f aca="false">IFERROR(C11/$C$16*100,"")</f>
+        <v>3.76129918739628</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>22362</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <f aca="false">IFERROR(C12/$C$16*100,"")</f>
+        <v>2.27940846689853</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>18795</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <f aca="false">IFERROR(C13/$C$16*100,"")</f>
+        <v>1.91581621211689</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>8603</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <f aca="false">IFERROR(C14/$C$16*100,"")</f>
+        <v>0.876922951468028</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <f aca="false">IFERROR(C15/$C$16*100,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>4412</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <f aca="false">Resumen!B7</f>
+        <v>981044</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <f aca="false">IFERROR(C16/$C$16*100,"")</f>
         <v>100</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>189</v>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3091,7 +3232,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -3100,10 +3241,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>60</v>
       </c>
@@ -3114,344 +3255,104 @@
         <v>52</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>191</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>192</v>
+        <v>238</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>45</v>
+        <v>491</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>6065</v>
+        <v>102369</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">IFERROR(C4/$C$25*100,"")</f>
-        <v>5.92470303219756</v>
+        <f aca="false">IFERROR(C4/$C$9*100,"")</f>
+        <v>46.2371273712737</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>193</v>
+        <v>239</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1155</v>
+        <v>48473</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">IFERROR(C5/$C$25*100,"")</f>
-        <v>1.12828227571116</v>
+        <f aca="false">IFERROR(C5/$C$9*100,"")</f>
+        <v>21.8938572719061</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>194</v>
+        <v>240</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9680</v>
+        <v>2306</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">IFERROR(C6/$C$25*100,"")</f>
-        <v>9.45608002500782</v>
+        <f aca="false">IFERROR(C6/$C$9*100,"")</f>
+        <v>1.04155374887082</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>195</v>
+        <v>241</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3</v>
+        <v>179</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>214</v>
+        <v>32260</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">IFERROR(C7/$C$25*100,"")</f>
-        <v>0.209049703032198</v>
+        <f aca="false">IFERROR(C7/$C$9*100,"")</f>
+        <v>14.5709123757904</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>196</v>
+        <v>242</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>12719</v>
+        <v>35992</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">IFERROR(C8/$C$25*100,"")</f>
-        <v>12.4247811816193</v>
+        <f aca="false">IFERROR(C8/$C$9*100,"")</f>
+        <v>16.256549232159</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>17580</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <f aca="false">IFERROR(C9/$C$25*100,"")</f>
-        <v>17.1733354173179</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>8272</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <f aca="false">IFERROR(C10/$C$25*100,"")</f>
-        <v>8.0806502031885</v>
+      <c r="A9" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <f aca="false">SUM(B4:B8)</f>
+        <v>1086</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <f aca="false">SUM(C4:C8)</f>
+        <v>221400</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <f aca="false">SUM(D4:D8)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>5589</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <f aca="false">IFERROR(C11/$C$25*100,"")</f>
-        <v>5.4597139731166</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1866</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <f aca="false">IFERROR(C12/$C$25*100,"")</f>
-        <v>1.82283526101907</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>877</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <f aca="false">IFERROR(C13/$C$25*100,"")</f>
-        <v>0.856713035323539</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>396</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <f aca="false">IFERROR(C14/$C$25*100,"")</f>
-        <v>0.386839637386683</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>2257</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <f aca="false">IFERROR(C15/$C$25*100,"")</f>
-        <v>2.20479055954986</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>8898</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <f aca="false">IFERROR(C16/$C$25*100,"")</f>
-        <v>8.69216942794623</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>4761</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <f aca="false">IFERROR(C17/$C$25*100,"")</f>
-        <v>4.65086745858081</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>5640</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <f aca="false">IFERROR(C18/$C$25*100,"")</f>
-        <v>5.5095342294467</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>4925</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <f aca="false">IFERROR(C19/$C$25*100,"")</f>
-        <v>4.81107377305408</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>1213</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <f aca="false">IFERROR(C20/$C$25*100,"")</f>
-        <v>1.18494060643951</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>4527</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <f aca="false">IFERROR(C21/$C$25*100,"")</f>
-        <v>4.42228040012504</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>5345</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <f aca="false">IFERROR(C22/$C$25*100,"")</f>
-        <v>5.22135823694905</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>256</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <f aca="false">IFERROR(C23/$C$25*100,"")</f>
-        <v>0.250078149421694</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>133</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <f aca="false">IFERROR(C24/$C$25*100,"")</f>
-        <v>0.12992341356674</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="8" t="n">
-        <f aca="false">SUM(B4:B24)</f>
-        <v>491</v>
-      </c>
-      <c r="C25" s="8" t="n">
-        <f aca="false">SUM(C4:C24)</f>
-        <v>102368</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <f aca="false">SUM(D4:D24)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10" t="s">
-        <v>212</v>
+      <c r="A11" s="10" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -3588,7 +3489,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -3597,7 +3498,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3611,119 +3512,344 @@
         <v>52</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>164</v>
+        <v>45</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>38135</v>
+        <v>6065</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">IFERROR(C4/$C$10*100,"")</f>
-        <v>37.2528524538918</v>
+        <f aca="false">IFERROR(C4/$C$25*100,"")</f>
+        <v>5.92470303219756</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>24029</v>
+        <v>1155</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">IFERROR(C5/$C$10*100,"")</f>
-        <v>23.473155673648</v>
+        <f aca="false">IFERROR(C5/$C$25*100,"")</f>
+        <v>1.12828227571116</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6405</v>
+        <v>9680</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">IFERROR(C6/$C$10*100,"")</f>
-        <v>6.25683807439825</v>
+        <f aca="false">IFERROR(C6/$C$25*100,"")</f>
+        <v>9.45608002500782</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>12449</v>
+        <v>214</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">IFERROR(C7/$C$10*100,"")</f>
-        <v>12.1610268834011</v>
+        <f aca="false">IFERROR(C7/$C$25*100,"")</f>
+        <v>0.209049703032198</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>620</v>
+        <v>12719</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">IFERROR(C8/$C$10*100,"")</f>
-        <v>0.605658018130666</v>
+        <f aca="false">IFERROR(C8/$C$25*100,"")</f>
+        <v>12.4247811816193</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>20730</v>
+        <v>17580</v>
       </c>
       <c r="D9" s="5" t="n">
-        <f aca="false">IFERROR(C9/$C$10*100,"")</f>
-        <v>20.2504688965302</v>
+        <f aca="false">IFERROR(C9/$C$25*100,"")</f>
+        <v>17.1733354173179</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>8272</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <f aca="false">IFERROR(C10/$C$25*100,"")</f>
+        <v>8.0806502031885</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>5589</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <f aca="false">IFERROR(C11/$C$25*100,"")</f>
+        <v>5.4597139731166</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1866</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <f aca="false">IFERROR(C12/$C$25*100,"")</f>
+        <v>1.82283526101907</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>877</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <f aca="false">IFERROR(C13/$C$25*100,"")</f>
+        <v>0.856713035323539</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>396</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <f aca="false">IFERROR(C14/$C$25*100,"")</f>
+        <v>0.386839637386683</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>2257</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <f aca="false">IFERROR(C15/$C$25*100,"")</f>
+        <v>2.20479055954986</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>8898</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <f aca="false">IFERROR(C16/$C$25*100,"")</f>
+        <v>8.69216942794623</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>4761</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <f aca="false">IFERROR(C17/$C$25*100,"")</f>
+        <v>4.65086745858081</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>5640</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <f aca="false">IFERROR(C18/$C$25*100,"")</f>
+        <v>5.5095342294467</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>4925</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <f aca="false">IFERROR(C19/$C$25*100,"")</f>
+        <v>4.81107377305408</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>1213</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <f aca="false">IFERROR(C20/$C$25*100,"")</f>
+        <v>1.18494060643951</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>4527</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <f aca="false">IFERROR(C21/$C$25*100,"")</f>
+        <v>4.42228040012504</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>5345</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <f aca="false">IFERROR(C22/$C$25*100,"")</f>
+        <v>5.22135823694905</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>256</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <f aca="false">IFERROR(C23/$C$25*100,"")</f>
+        <v>0.250078149421694</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <f aca="false">IFERROR(C24/$C$25*100,"")</f>
+        <v>0.12992341356674</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="8" t="n">
-        <f aca="false">SUM(B4:B9)</f>
+      <c r="B25" s="8" t="n">
+        <f aca="false">SUM(B4:B24)</f>
         <v>491</v>
       </c>
-      <c r="C10" s="8" t="n">
-        <f aca="false">SUM(C4:C9)</f>
+      <c r="C25" s="8" t="n">
+        <f aca="false">SUM(C4:C24)</f>
         <v>102368</v>
       </c>
-      <c r="D10" s="9" t="n">
-        <f aca="false">SUM(D4:D9)</f>
+      <c r="D25" s="9" t="n">
+        <f aca="false">SUM(D4:D24)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>220</v>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3751,7 +3877,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3765,97 +3891,97 @@
         <v>52</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>10</v>
+        <v>164</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1930</v>
+        <v>38135</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">IFERROR(C4/$C$10*100,"")</f>
-        <v>1.88535479837449</v>
+        <v>37.2528524538918</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>18528</v>
+        <v>24029</v>
       </c>
       <c r="D5" s="5" t="n">
         <f aca="false">IFERROR(C5/$C$10*100,"")</f>
-        <v>18.0994060643951</v>
+        <v>23.473155673648</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>332</v>
+        <v>29</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>71521</v>
+        <v>6405</v>
       </c>
       <c r="D6" s="5" t="n">
         <f aca="false">IFERROR(C6/$C$10*100,"")</f>
-        <v>69.866559862457</v>
+        <v>6.25683807439825</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5710</v>
+        <v>12449</v>
       </c>
       <c r="D7" s="5" t="n">
         <f aca="false">IFERROR(C7/$C$10*100,"")</f>
-        <v>5.5779149734292</v>
+        <v>12.1610268834011</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>226</v>
+        <v>272</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4408</v>
+        <v>620</v>
       </c>
       <c r="D8" s="5" t="n">
         <f aca="false">IFERROR(C8/$C$10*100,"")</f>
-        <v>4.3060331353548</v>
+        <v>0.605658018130666</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>227</v>
+        <v>273</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>271</v>
+        <v>20730</v>
       </c>
       <c r="D9" s="5" t="n">
         <f aca="false">IFERROR(C9/$C$10*100,"")</f>
-        <v>0.264731165989372</v>
+        <v>20.2504688965302</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3877,7 +4003,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -3896,7 +4022,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -3905,7 +4031,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3919,59 +4045,119 @@
         <v>52</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>302</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>64679</v>
+        <v>1930</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">IFERROR(C4/$C$6*100,"")</f>
-        <v>63.1822133653743</v>
+        <f aca="false">IFERROR(C4/$C$10*100,"")</f>
+        <v>1.88535479837449</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>231</v>
+        <v>277</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>189</v>
+        <v>97</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>37690</v>
+        <v>18528</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">IFERROR(C5/$C$6*100,"")</f>
-        <v>36.8177866346257</v>
+        <f aca="false">IFERROR(C5/$C$10*100,"")</f>
+        <v>18.0994060643951</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>332</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>71521</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <f aca="false">IFERROR(C6/$C$10*100,"")</f>
+        <v>69.866559862457</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>5710</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <f aca="false">IFERROR(C7/$C$10*100,"")</f>
+        <v>5.5779149734292</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>4408</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <f aca="false">IFERROR(C8/$C$10*100,"")</f>
+        <v>4.3060331353548</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>271</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <f aca="false">IFERROR(C9/$C$10*100,"")</f>
+        <v>0.264731165989372</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="8" t="n">
-        <f aca="false">SUM(B4:B5)</f>
+      <c r="B10" s="8" t="n">
+        <f aca="false">SUM(B4:B9)</f>
         <v>491</v>
       </c>
-      <c r="C6" s="8" t="n">
-        <f aca="false">SUM(C4:C5)</f>
-        <v>102369</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <f aca="false">SUM(D4:D5)</f>
+      <c r="C10" s="8" t="n">
+        <f aca="false">SUM(C4:C9)</f>
+        <v>102368</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <f aca="false">SUM(D4:D9)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>232</v>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -3990,6 +4176,100 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>302</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>64679</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <f aca="false">IFERROR(C4/$C$6*100,"")</f>
+        <v>63.1822133653743</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>189</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>37690</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <f aca="false">IFERROR(C5/$C$6*100,"")</f>
+        <v>36.8177866346257</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="8" t="n">
+        <f aca="false">SUM(B4:B5)</f>
+        <v>491</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <f aca="false">SUM(C4:C5)</f>
+        <v>102369</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <f aca="false">SUM(D4:D5)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -3999,7 +4279,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4013,12 +4293,12 @@
         <v>52</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>234</v>
+        <v>288</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>366</v>
@@ -4033,7 +4313,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>235</v>
+        <v>289</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>103</v>
@@ -4048,7 +4328,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>236</v>
+        <v>290</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>22</v>
@@ -4080,7 +4360,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>237</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -4978,7 +5258,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -5015,21 +5295,21 @@
         <v>97</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>21184</v>
+        <v>12843</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">IFERROR(C4/$C$12*100,"")</f>
-        <v>2.15933230313829</v>
+        <f aca="false">IFERROR(C4/$C$56*100,"")</f>
+        <v>1.30911292640712</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>254785</v>
+        <v>128735</v>
       </c>
       <c r="F4" s="5" t="n">
         <f aca="false">IFERROR(C4/E4*100,"")</f>
-        <v>8.31446121239477</v>
+        <v>9.97630791936925</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5037,21 +5317,21 @@
         <v>98</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>690</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>130680</v>
+        <v>124</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">IFERROR(C5/$C$12*100,"")</f>
-        <v>13.3205034636571</v>
+        <f aca="false">IFERROR(C5/$C$56*100,"")</f>
+        <v>0.012639570417697</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1470155</v>
+        <v>882</v>
       </c>
       <c r="F5" s="5" t="n">
         <f aca="false">IFERROR(C5/E5*100,"")</f>
-        <v>8.88885865776058</v>
+        <v>14.0589569160998</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5059,21 +5339,21 @@
         <v>99</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2081</v>
+        <v>81</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>466797</v>
+        <v>16361</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">IFERROR(C6/$C$12*100,"")</f>
-        <v>47.5816579072906</v>
+        <f aca="false">IFERROR(C6/$C$56*100,"")</f>
+        <v>1.66770977099952</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4214733</v>
+        <v>199456</v>
       </c>
       <c r="F6" s="5" t="n">
         <f aca="false">IFERROR(C6/E6*100,"")</f>
-        <v>11.0753634927764</v>
+        <v>8.20281164768169</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5081,21 +5361,21 @@
         <v>100</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>549</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>127450</v>
+        <v>474</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">IFERROR(C7/$C$12*100,"")</f>
-        <v>12.9912623694758</v>
+        <f aca="false">IFERROR(C7/$C$56*100,"")</f>
+        <v>0.0483157772418419</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1423225</v>
+        <v>16036</v>
       </c>
       <c r="F7" s="5" t="n">
         <f aca="false">IFERROR(C7/E7*100,"")</f>
-        <v>8.95501414042052</v>
+        <v>2.95584933898728</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5103,21 +5383,21 @@
         <v>101</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>921</v>
+        <v>75</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>220323</v>
+        <v>16065</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">IFERROR(C8/$C$12*100,"")</f>
-        <v>22.4580141155748</v>
+        <f aca="false">IFERROR(C8/$C$56*100,"")</f>
+        <v>1.63753789322825</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2625074</v>
+        <v>258584</v>
       </c>
       <c r="F8" s="5" t="n">
         <f aca="false">IFERROR(C8/E8*100,"")</f>
-        <v>8.39302053961146</v>
+        <v>6.21268137239736</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5125,21 +5405,21 @@
         <v>102</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>10491</v>
+        <v>8435</v>
       </c>
       <c r="D9" s="5" t="n">
-        <f aca="false">IFERROR(C9/$C$12*100,"")</f>
-        <v>1.06937099661177</v>
+        <f aca="false">IFERROR(C9/$C$56*100,"")</f>
+        <v>0.859796584461891</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>254452</v>
+        <v>115065</v>
       </c>
       <c r="F9" s="5" t="n">
         <f aca="false">IFERROR(C9/E9*100,"")</f>
-        <v>4.12297800763995</v>
+        <v>7.33063920392821</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5147,21 +5427,21 @@
         <v>103</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2352</v>
+        <v>1037</v>
       </c>
       <c r="D10" s="5" t="n">
-        <f aca="false">IFERROR(C10/$C$12*100,"")</f>
-        <v>0.239744598611275</v>
+        <f aca="false">IFERROR(C10/$C$56*100,"")</f>
+        <v>0.105703504218966</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>34102</v>
+        <v>17999</v>
       </c>
       <c r="F10" s="5" t="n">
         <f aca="false">IFERROR(C10/E10*100,"")</f>
-        <v>6.89695619025277</v>
+        <v>5.7614311906217</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5169,51 +5449,1019 @@
         <v>104</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1767</v>
+        <v>10482</v>
       </c>
       <c r="D11" s="5" t="n">
-        <f aca="false">IFERROR(C11/$C$12*100,"")</f>
-        <v>0.180114245640359</v>
+        <f aca="false">IFERROR(C11/$C$56*100,"")</f>
+        <v>1.06845142837339</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>18534</v>
+        <v>112407</v>
       </c>
       <c r="F11" s="5" t="n">
         <f aca="false">IFERROR(C11/E11*100,"")</f>
-        <v>9.53382971835545</v>
+        <v>9.32504203474873</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>1092</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <f aca="false">IFERROR(C12/$C$56*100,"")</f>
+        <v>0.111309765291332</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>14663</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <f aca="false">IFERROR(C12/E12*100,"")</f>
+        <v>7.44731637454818</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>3956</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <f aca="false">IFERROR(C13/$C$56*100,"")</f>
+        <v>0.403243069132334</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>42680</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <f aca="false">IFERROR(C13/E13*100,"")</f>
+        <v>9.26897844423618</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>166</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>30999</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <f aca="false">IFERROR(C14/$C$56*100,"")</f>
+        <v>3.15979067240476</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>294032</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <f aca="false">IFERROR(C14/E14*100,"")</f>
+        <v>10.5427300429885</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>2640</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <f aca="false">IFERROR(C15/$C$56*100,"")</f>
+        <v>0.26910053147355</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>48001</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <f aca="false">IFERROR(C15/E15*100,"")</f>
+        <v>5.49988541905377</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>6961</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <f aca="false">IFERROR(C16/$C$56*100,"")</f>
+        <v>0.709548787722492</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>86683</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <f aca="false">IFERROR(C16/E16*100,"")</f>
+        <v>8.03040965356529</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>254</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>41500</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <f aca="false">IFERROR(C17/$C$56*100,"")</f>
+        <v>4.2301788091486</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>428490</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <f aca="false">IFERROR(C17/E17*100,"")</f>
+        <v>9.68517351630143</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>9710</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <f aca="false">IFERROR(C18/$C$56*100,"")</f>
+        <v>0.989759909321276</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>66163</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <f aca="false">IFERROR(C18/E18*100,"")</f>
+        <v>14.6758762450312</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>4497</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <f aca="false">IFERROR(C19/$C$56*100,"")</f>
+        <v>0.458388291680512</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>45133</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <f aca="false">IFERROR(C19/E19*100,"")</f>
+        <v>9.96388451908803</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B12" s="8" t="n">
-        <f aca="false">SUM(B4:B11)</f>
+      <c r="C20" s="4" t="n">
+        <v>12908</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <f aca="false">IFERROR(C20/$C$56*100,"")</f>
+        <v>1.31573850767446</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>108975</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <f aca="false">IFERROR(C20/E20*100,"")</f>
+        <v>11.8449185593026</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>7022</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <f aca="false">IFERROR(C21/$C$56*100,"")</f>
+        <v>0.715766640911843</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>92087</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <f aca="false">IFERROR(C21/E21*100,"")</f>
+        <v>7.62539772171968</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>8101</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <f aca="false">IFERROR(C22/$C$56*100,"")</f>
+        <v>0.825751289949707</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>86839</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <f aca="false">IFERROR(C22/E22*100,"")</f>
+        <v>9.32875781618858</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>22865</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <f aca="false">IFERROR(C23/$C$56*100,"")</f>
+        <v>2.33067562581163</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>199298</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <f aca="false">IFERROR(C23/E23*100,"")</f>
+        <v>11.4727694206665</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>615</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>311298</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <f aca="false">IFERROR(C24/$C$56*100,"")</f>
+        <v>31.7312338055504</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>3430713</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <f aca="false">IFERROR(C24/E24*100,"")</f>
+        <v>9.07385724192027</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>50055</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <f aca="false">IFERROR(C25/$C$56*100,"")</f>
+        <v>5.1022072359502</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>387682</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <f aca="false">IFERROR(C25/E25*100,"")</f>
+        <v>12.9113551828561</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>17146</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <f aca="false">IFERROR(C26/$C$56*100,"")</f>
+        <v>1.74772640630511</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>204500</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <f aca="false">IFERROR(C26/E26*100,"")</f>
+        <v>8.38435207823961</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>31215</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <f aca="false">IFERROR(C27/$C$56*100,"")</f>
+        <v>3.18180798861623</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>297820</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <f aca="false">IFERROR(C27/E27*100,"")</f>
+        <v>10.4811631186623</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>7101</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <f aca="false">IFERROR(C28/$C$56*100,"")</f>
+        <v>0.72381927045215</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>95659</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <f aca="false">IFERROR(C28/E28*100,"")</f>
+        <v>7.42324297766023</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>18684</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <f aca="false">IFERROR(C29/$C$56*100,"")</f>
+        <v>1.90449785229235</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>171805</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <f aca="false">IFERROR(C29/E29*100,"")</f>
+        <v>10.8751200488926</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>193</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>37690</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <f aca="false">IFERROR(C30/$C$56*100,"")</f>
+        <v>3.84181781486291</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>349230</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <f aca="false">IFERROR(C30/E30*100,"")</f>
+        <v>10.7923145205166</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>1782</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <f aca="false">IFERROR(C31/$C$56*100,"")</f>
+        <v>0.181642858744646</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>21139</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <f aca="false">IFERROR(C31/E31*100,"")</f>
+        <v>8.42991626850844</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>11562</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <f aca="false">IFERROR(C32/$C$56*100,"")</f>
+        <v>1.17853800943075</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>115858</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <f aca="false">IFERROR(C32/E32*100,"")</f>
+        <v>9.97945761190423</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>22137</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <f aca="false">IFERROR(C33/$C$56*100,"")</f>
+        <v>2.25646911561741</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>220137</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <f aca="false">IFERROR(C33/E33*100,"")</f>
+        <v>10.0560105752327</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>2904</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <f aca="false">IFERROR(C34/$C$56*100,"")</f>
+        <v>0.296010584620905</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>27680</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <f aca="false">IFERROR(C34/E34*100,"")</f>
+        <v>10.4913294797688</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>13989</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <f aca="false">IFERROR(C35/$C$56*100,"")</f>
+        <v>1.42592702075132</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>152871</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <f aca="false">IFERROR(C35/E35*100,"")</f>
+        <v>9.15085267971035</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>16346</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <f aca="false">IFERROR(C36/$C$56*100,"")</f>
+        <v>1.66618079070706</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>150919</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <f aca="false">IFERROR(C36/E36*100,"")</f>
+        <v>10.8309755564243</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>18194</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <f aca="false">IFERROR(C37/$C$56*100,"")</f>
+        <v>1.85455116273855</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>170036</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <f aca="false">IFERROR(C37/E37*100,"")</f>
+        <v>10.7000870403914</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>2720</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <f aca="false">IFERROR(C38/$C$56*100,"")</f>
+        <v>0.277255093033354</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>22322</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <f aca="false">IFERROR(C38/E38*100,"")</f>
+        <v>12.1852880566258</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>5978</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <f aca="false">IFERROR(C39/$C$56*100,"")</f>
+        <v>0.609349612556394</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>52985</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <f aca="false">IFERROR(C39/E39*100,"")</f>
+        <v>11.2824384259696</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>52663</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <f aca="false">IFERROR(C40/$C$56*100,"")</f>
+        <v>5.36804594279983</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>514395</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <f aca="false">IFERROR(C40/E40*100,"")</f>
+        <v>10.237852234178</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>8420</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <f aca="false">IFERROR(C41/$C$56*100,"")</f>
+        <v>0.858267604169427</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>79943</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <f aca="false">IFERROR(C41/E41*100,"")</f>
+        <v>10.5325044093917</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>22040</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <f aca="false">IFERROR(C42/$C$56*100,"")</f>
+        <v>2.24658170972615</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>189036</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <f aca="false">IFERROR(C42/E42*100,"")</f>
+        <v>11.6591548699719</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>36547</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <f aca="false">IFERROR(C43/$C$56*100,"")</f>
+        <v>3.7253095165772</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>387282</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <f aca="false">IFERROR(C43/E43*100,"")</f>
+        <v>9.43679282796515</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>11650</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <f aca="false">IFERROR(C44/$C$56*100,"")</f>
+        <v>1.18750802714654</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>94767</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <f aca="false">IFERROR(C44/E44*100,"")</f>
+        <v>12.2933088522376</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>16961</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <f aca="false">IFERROR(C45/$C$56*100,"")</f>
+        <v>1.72886898269806</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>155985</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <f aca="false">IFERROR(C45/E45*100,"")</f>
+        <v>10.8734814244959</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>4269</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <f aca="false">IFERROR(C46/$C$56*100,"")</f>
+        <v>0.43514779123507</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>44820</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <f aca="false">IFERROR(C46/E46*100,"")</f>
+        <v>9.52476572958501</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>143</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>21327</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <f aca="false">IFERROR(C47/$C$56*100,"")</f>
+        <v>2.17390417982439</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>229174</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <f aca="false">IFERROR(C47/E47*100,"")</f>
+        <v>9.30602947978392</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>4378</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <f aca="false">IFERROR(C48/$C$56*100,"")</f>
+        <v>0.446258381360303</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>87058</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <f aca="false">IFERROR(C48/E48*100,"")</f>
+        <v>5.0288313538101</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>7304</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <f aca="false">IFERROR(C49/$C$56*100,"")</f>
+        <v>0.744511470410154</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>114108</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <f aca="false">IFERROR(C49/E49*100,"")</f>
+        <v>6.40095348266554</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>1472</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <f aca="false">IFERROR(C50/$C$56*100,"")</f>
+        <v>0.150043932700403</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>35206</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <f aca="false">IFERROR(C50/E50*100,"")</f>
+        <v>4.18110549338181</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>611</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <f aca="false">IFERROR(C51/$C$56*100,"")</f>
+        <v>0.0622804639130071</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>17956</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <f aca="false">IFERROR(C51/E51*100,"")</f>
+        <v>3.40276230786367</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>243</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <f aca="false">IFERROR(C52/$C$56*100,"")</f>
+        <v>0.0247694807379063</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>4031</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <f aca="false">IFERROR(C52/E52*100,"")</f>
+        <v>6.02828082361697</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>5149</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <f aca="false">IFERROR(C53/$C$56*100,"")</f>
+        <v>0.524847968392919</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>83468</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <f aca="false">IFERROR(C53/E53*100,"")</f>
+        <v>6.16883116883117</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <f aca="false">IFERROR(C54/$C$56*100,"")</f>
+        <v>0.0100912699302581</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>5123</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <f aca="false">IFERROR(C54/E54*100,"")</f>
+        <v>1.9324614483701</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <f aca="false">IFERROR(C55/$C$56*100,"")</f>
+        <v>0.106009300277459</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>16787</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <f aca="false">IFERROR(C55/E55*100,"")</f>
+        <v>6.19527014952046</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56" s="8" t="n">
+        <f aca="false">SUM(B4:B55)</f>
         <v>4412</v>
       </c>
-      <c r="C12" s="8" t="n">
-        <f aca="false">SUM(C4:C11)</f>
-        <v>981044</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <f aca="false">SUM(D4:D11)</f>
+      <c r="C56" s="8" t="n">
+        <f aca="false">SUM(C4:C55)</f>
+        <v>981046</v>
+      </c>
+      <c r="D56" s="9" t="n">
+        <f aca="false">SUM(D4:D55)</f>
         <v>100</v>
       </c>
-      <c r="E12" s="8" t="n">
-        <f aca="false">SUM(E4:E11)</f>
-        <v>10295060</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <f aca="false">IFERROR(C12/E12*100,"")</f>
-        <v>9.52926937774039</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>105</v>
+      <c r="E56" s="8" t="n">
+        <f aca="false">SUM(E4:E55)</f>
+        <v>10292703</v>
+      </c>
+      <c r="F56" s="9" t="n">
+        <f aca="false">IFERROR(C56/E56*100,"")</f>
+        <v>9.53147098483265</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="10" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -5232,7 +6480,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -5241,7 +6489,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5266,71 +6514,208 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>4211</v>
+        <v>131</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>910039</v>
+        <v>21184</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">IFERROR(C4/$C$6*100,"")</f>
-        <v>92.7623022005129</v>
+        <f aca="false">IFERROR(C4/$C$12*100,"")</f>
+        <v>2.15933230313829</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>9197979</v>
+        <v>254785</v>
       </c>
       <c r="F4" s="5" t="n">
         <f aca="false">IFERROR(C4/E4*100,"")</f>
-        <v>9.89390169296973</v>
+        <v>8.31446121239477</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>201</v>
+        <v>690</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>71005</v>
+        <v>130680</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">IFERROR(C5/$C$6*100,"")</f>
-        <v>7.23769779948708</v>
+        <f aca="false">IFERROR(C5/$C$12*100,"")</f>
+        <v>13.3205034636571</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1097082</v>
+        <v>1470155</v>
       </c>
       <c r="F5" s="5" t="n">
         <f aca="false">IFERROR(C5/E5*100,"")</f>
-        <v>6.47216889895195</v>
+        <v>8.88885865776058</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>2081</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>466797</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <f aca="false">IFERROR(C6/$C$12*100,"")</f>
+        <v>47.5816579072906</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>4214733</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <f aca="false">IFERROR(C6/E6*100,"")</f>
+        <v>11.0753634927764</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>549</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>127450</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <f aca="false">IFERROR(C7/$C$12*100,"")</f>
+        <v>12.9912623694758</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>1423225</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <f aca="false">IFERROR(C7/E7*100,"")</f>
+        <v>8.95501414042052</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>921</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>220323</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <f aca="false">IFERROR(C8/$C$12*100,"")</f>
+        <v>22.4580141155748</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>2625074</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <f aca="false">IFERROR(C8/E8*100,"")</f>
+        <v>8.39302053961146</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>10491</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <f aca="false">IFERROR(C9/$C$12*100,"")</f>
+        <v>1.06937099661177</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>254452</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <f aca="false">IFERROR(C9/E9*100,"")</f>
+        <v>4.12297800763995</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2352</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <f aca="false">IFERROR(C10/$C$12*100,"")</f>
+        <v>0.239744598611275</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>34102</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <f aca="false">IFERROR(C10/E10*100,"")</f>
+        <v>6.89695619025277</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1767</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <f aca="false">IFERROR(C11/$C$12*100,"")</f>
+        <v>0.180114245640359</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>18534</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <f aca="false">IFERROR(C11/E11*100,"")</f>
+        <v>9.53382971835545</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="8" t="n">
-        <f aca="false">SUM(B4:B5)</f>
+      <c r="B12" s="8" t="n">
+        <f aca="false">SUM(B4:B11)</f>
         <v>4412</v>
       </c>
-      <c r="C6" s="8" t="n">
-        <f aca="false">SUM(C4:C5)</f>
+      <c r="C12" s="8" t="n">
+        <f aca="false">SUM(C4:C11)</f>
         <v>981044</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <f aca="false">SUM(D4:D5)</f>
+      <c r="D12" s="9" t="n">
+        <f aca="false">SUM(D4:D11)</f>
         <v>100</v>
       </c>
-      <c r="E6" s="8" t="n">
-        <f aca="false">SUM(E4:E5)</f>
-        <v>10295061</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <f aca="false">IFERROR(C6/E6*100,"")</f>
-        <v>9.52926845212476</v>
+      <c r="E12" s="8" t="n">
+        <f aca="false">SUM(E4:E11)</f>
+        <v>10295060</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <f aca="false">IFERROR(C12/E12*100,"")</f>
+        <v>9.52926937774039</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -5349,7 +6734,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -5358,7 +6743,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5383,92 +6768,70 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>667</v>
+        <v>4211</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>124991</v>
+        <v>910039</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">IFERROR(C4/$C$7*100,"")</f>
-        <v>12.7406110225433</v>
+        <f aca="false">IFERROR(C4/$C$6*100,"")</f>
+        <v>92.7623022005129</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1164249</v>
+        <v>9197979</v>
       </c>
       <c r="F4" s="5" t="n">
         <f aca="false">IFERROR(C4/E4*100,"")</f>
-        <v>10.7357618516314</v>
+        <v>9.89390169296973</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3736</v>
+        <v>201</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>854090</v>
+        <v>71005</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">IFERROR(C5/$C$7*100,"")</f>
-        <v>87.0592960152654</v>
+        <f aca="false">IFERROR(C5/$C$6*100,"")</f>
+        <v>7.23769779948708</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>9111186</v>
+        <v>1097082</v>
       </c>
       <c r="F5" s="5" t="n">
         <f aca="false">IFERROR(C5/E5*100,"")</f>
-        <v>9.37408148620827</v>
+        <v>6.47216889895195</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1963</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <f aca="false">IFERROR(C6/$C$7*100,"")</f>
-        <v>0.200092962191298</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>19626</v>
-      </c>
-      <c r="F6" s="5" t="n">
+      <c r="A6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="8" t="n">
+        <f aca="false">SUM(B4:B5)</f>
+        <v>4412</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <f aca="false">SUM(C4:C5)</f>
+        <v>981044</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <f aca="false">SUM(D4:D5)</f>
+        <v>100</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <f aca="false">SUM(E4:E5)</f>
+        <v>10295061</v>
+      </c>
+      <c r="F6" s="9" t="n">
         <f aca="false">IFERROR(C6/E6*100,"")</f>
-        <v>10.0020381127076</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="8" t="n">
-        <f aca="false">SUM(B4:B6)</f>
-        <v>4412</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <f aca="false">SUM(C4:C6)</f>
-        <v>981044</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <f aca="false">SUM(D4:D6)</f>
-        <v>100</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <f aca="false">SUM(E4:E6)</f>
-        <v>10295061</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <f aca="false">IFERROR(C7/E7*100,"")</f>
         <v>9.52926845212476</v>
       </c>
     </row>
@@ -5488,7 +6851,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -5497,7 +6860,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5522,70 +6885,92 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1343</v>
+        <v>667</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>301672</v>
+        <v>124991</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">IFERROR(C4/$C$6*100,"")</f>
-        <v>30.7500988742605</v>
+        <f aca="false">IFERROR(C4/$C$7*100,"")</f>
+        <v>12.7406110225433</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5537482</v>
+        <v>1164249</v>
       </c>
       <c r="F4" s="5" t="n">
         <f aca="false">IFERROR(C4/E4*100,"")</f>
-        <v>5.44781906288815</v>
+        <v>10.7357618516314</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3069</v>
+        <v>3736</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>679372</v>
+        <v>854090</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">IFERROR(C5/$C$6*100,"")</f>
-        <v>69.2499011257395</v>
+        <f aca="false">IFERROR(C5/$C$7*100,"")</f>
+        <v>87.0592960152654</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4757579</v>
+        <v>9111186</v>
       </c>
       <c r="F5" s="5" t="n">
         <f aca="false">IFERROR(C5/E5*100,"")</f>
-        <v>14.2797838984912</v>
+        <v>9.37408148620827</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1963</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <f aca="false">IFERROR(C6/$C$7*100,"")</f>
+        <v>0.200092962191298</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>19626</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <f aca="false">IFERROR(C6/E6*100,"")</f>
+        <v>10.0020381127076</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="8" t="n">
-        <f aca="false">SUM(B4:B5)</f>
+      <c r="B7" s="8" t="n">
+        <f aca="false">SUM(B4:B6)</f>
         <v>4412</v>
       </c>
-      <c r="C6" s="8" t="n">
-        <f aca="false">SUM(C4:C5)</f>
+      <c r="C7" s="8" t="n">
+        <f aca="false">SUM(C4:C6)</f>
         <v>981044</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <f aca="false">SUM(D4:D5)</f>
+      <c r="D7" s="9" t="n">
+        <f aca="false">SUM(D4:D6)</f>
         <v>100</v>
       </c>
-      <c r="E6" s="8" t="n">
-        <f aca="false">SUM(E4:E5)</f>
+      <c r="E7" s="8" t="n">
+        <f aca="false">SUM(E4:E6)</f>
         <v>10295061</v>
       </c>
-      <c r="F6" s="9" t="n">
-        <f aca="false">IFERROR(C6/E6*100,"")</f>
+      <c r="F7" s="9" t="n">
+        <f aca="false">IFERROR(C7/E7*100,"")</f>
         <v>9.52926845212476</v>
       </c>
     </row>
